--- a/data/Key_NIC_Codes_List.xlsx
+++ b/data/Key_NIC_Codes_List.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaide\Documents\MSME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C380746-CE16-4060-B3BF-F43EB00CDCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC01DC79-371D-45C5-A8C9-0D9F9560685F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2917915F-F473-4392-AA36-2031E66DDC32}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AAECC131-D26C-4426-BC68-209BB2D98673}"/>
   </bookViews>
   <sheets>
-    <sheet name="Key NIC Codes" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>NIC Code</t>
   </si>
@@ -47,43 +47,79 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Retail sale of readymade garments, hosiery goods, other articles of clothing and clothing accessories such as gloves, ties, braces etc.</t>
+    <t>Manufacture of knitted and crocheted cotton fabrics</t>
+  </si>
+  <si>
+    <t>Manufacture of knitted and crocheted woolen fabrics</t>
+  </si>
+  <si>
+    <t>Manufacture of knitted and crocheted synthetic fabrics</t>
+  </si>
+  <si>
+    <t>Manufacture of hats, caps and other clothing accessories such as gloves,</t>
+  </si>
+  <si>
+    <t>Manufacture of wearing apparel n.e.c.</t>
+  </si>
+  <si>
+    <t>Manufacture of fur and skin rugs and other similar articles</t>
+  </si>
+  <si>
+    <t>Manufacture of knitted or crocheted wearing apparel and other made-up</t>
+  </si>
+  <si>
+    <t>Manufacture of purse, ladies’ handbags, artistic leather presented articles</t>
+  </si>
+  <si>
+    <t>Manufacture of imitation jewellery and related articles</t>
+  </si>
+  <si>
+    <t>Wholesale of edible oils, fats, sugar and processed/manufactured spices</t>
+  </si>
+  <si>
+    <t>Wholesale of tea, coffee &amp; cocoa</t>
+  </si>
+  <si>
+    <t>Wholesale of textiles, fabrics, yarn, household linen, articles of clothing,</t>
+  </si>
+  <si>
+    <t>Wholesale of umbrella and clothing accessories</t>
+  </si>
+  <si>
+    <t>Wholesale of footwear</t>
+  </si>
+  <si>
+    <t>Wholesale of other clothing items n.e.c.</t>
+  </si>
+  <si>
+    <t>Other retail sale in non-specialized stores</t>
+  </si>
+  <si>
+    <t>Retail sale of cereals and pulses, tea, coffee, spices and flour</t>
+  </si>
+  <si>
+    <t>Retail sale of bakery products, dairy products and eggs</t>
+  </si>
+  <si>
+    <t>Retail sale of sugar confectionery and sweetmeat</t>
+  </si>
+  <si>
+    <t>Retail sale of other food products n.e.c.</t>
+  </si>
+  <si>
+    <t>Retail sale of textiles in specialized stores</t>
   </si>
   <si>
     <t>Retail sale of carpets, rugs, curtains and net curtains</t>
   </si>
   <si>
-    <t>Wholesale of other clothing items n.e.c.</t>
-  </si>
-  <si>
-    <t>Manufacture of knitted and crocheted cotton fabrics</t>
-  </si>
-  <si>
-    <t>Manufacture of knitted and crocheted woolen fabrics</t>
-  </si>
-  <si>
-    <t>Manufacture of knitted and crocheted synthetic fabrics</t>
-  </si>
-  <si>
-    <t>Manufacture of wearing apparel n.e.c.</t>
-  </si>
-  <si>
-    <t>Manufacture of knitted or crocheted wearing apparel and other made-up articles directly into shape (pullovers, cardigans, jerseys, waistcoats and similar articles)</t>
-  </si>
-  <si>
-    <t>Manufacture of purse, ladies' handbags, artistic leather presented articles and novelties</t>
-  </si>
-  <si>
-    <t>Wholesale of edible oils, fats, sugar and processed/manufactured spices etc.</t>
-  </si>
-  <si>
-    <t>Retail sale of cereals and pulses, tea, coffee, spices and flour</t>
-  </si>
-  <si>
-    <t>Retail sale of sugar confectionery and sweetmeat</t>
-  </si>
-  <si>
-    <t>Retail sale of other food products n.e.c.</t>
+    <t>Retail sale of wallpaper and floor coverings</t>
+  </si>
+  <si>
+    <t>Retail sale of household utensils and cutlery, crockery, glassware, china and</t>
+  </si>
+  <si>
+    <t>Retail sale of readymade garments, hosiery goods, other articles of clothing</t>
   </si>
   <si>
     <t>Retail sale of footwear</t>
@@ -92,52 +128,19 @@
     <t>Retail sale of perfumery and cosmetic articles</t>
   </si>
   <si>
+    <t>Retail sale of watches and clocks</t>
+  </si>
+  <si>
+    <t>Retail sale of jewellery and immitation jewellery</t>
+  </si>
+  <si>
+    <t>Retail sale of flowers, plants, pet animals and pet food</t>
+  </si>
+  <si>
     <t>Retail sale of souvenirs, craftwork and religious articles, stamps and coins</t>
   </si>
   <si>
-    <t>Manufacture of imitation jewellery and related articles</t>
-  </si>
-  <si>
-    <t>Wholesale of tea, coffee &amp; cocoa</t>
-  </si>
-  <si>
-    <t>Retail sale of jewellery and immitation jewellery</t>
-  </si>
-  <si>
-    <t>Manufacture of hats, caps and other clothing accessories such as gloves, belts, ties, cravats, hairnets etc.</t>
-  </si>
-  <si>
-    <t>Wholesale of textiles, fabrics, yarn, household linen, articles of clothing,</t>
-  </si>
-  <si>
-    <t>Wholesale of umbrella and clothing accessories</t>
-  </si>
-  <si>
-    <t>Wholesale of footwear</t>
-  </si>
-  <si>
-    <t>Wholesale trade via e-commerce excluding activities of commission agents</t>
-  </si>
-  <si>
-    <t>Retail sale of bakery products, dairy products and eggs</t>
-  </si>
-  <si>
-    <t>Retail sale of wallpaper and floor coverings</t>
-  </si>
-  <si>
-    <t>Retail sale of flowers, plants, pet animals and pet food</t>
-  </si>
-  <si>
     <t>Retail sale via stalls and markets of textiles, clothing and footwear</t>
-  </si>
-  <si>
-    <t>Retail sale via mail order houses</t>
-  </si>
-  <si>
-    <t>Retail sale via e-commerce</t>
-  </si>
-  <si>
-    <t>Other retail sale not in stores, stalls or markets</t>
   </si>
 </sst>
 </file>
@@ -173,8 +176,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,12 +514,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBADE600-883B-4D39-AACA-C96A663A8985}">
-  <dimension ref="A1:B32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3AEE108-8FA3-4687-9EC9-0091973CB9BA}">
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="131.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="62.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -525,251 +531,259 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>13911</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>13912</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>13913</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>14103</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>13912</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>14109</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>13913</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>14202</v>
+      </c>
+      <c r="B7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>14103</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>14301</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>15122</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>32120</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>46411</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>46412</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46413</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46419</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>47190</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>47211</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>47214</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>47215</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>47219</v>
+      </c>
+      <c r="B21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>14109</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>14301</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>15122</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>32120</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>46305</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>46306</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>46411</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>47510</v>
+      </c>
+      <c r="B22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>46412</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>47531</v>
+      </c>
+      <c r="B23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>46413</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>47532</v>
+      </c>
+      <c r="B24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>46419</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>46901</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>47592</v>
+      </c>
+      <c r="B25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>47211</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>47214</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>47711</v>
+      </c>
+      <c r="B26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>47215</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>47219</v>
-      </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>47531</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>47532</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>47713</v>
+      </c>
+      <c r="B27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>47711</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>47713</v>
-      </c>
-      <c r="B24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
         <v>47722</v>
       </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>47733</v>
-      </c>
-      <c r="B26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>47734</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>47735</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
-      </c>
-    </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>47820</v>
+      <c r="A29" s="1">
+        <v>47732</v>
       </c>
       <c r="B29" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>47911</v>
+      <c r="A30" s="1">
+        <v>47733</v>
       </c>
       <c r="B30" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>47912</v>
+      <c r="A31" s="1">
+        <v>47734</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>47990</v>
+      <c r="A32" s="1">
+        <v>47735</v>
       </c>
       <c r="B32" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>47820</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/Key_NIC_Codes_List.xlsx
+++ b/data/Key_NIC_Codes_List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaide\Documents\MSME\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaide\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC01DC79-371D-45C5-A8C9-0D9F9560685F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B664A500-CD48-4FE8-859C-9A65315C07AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AAECC131-D26C-4426-BC68-209BB2D98673}"/>
   </bookViews>
@@ -56,33 +56,18 @@
     <t>Manufacture of knitted and crocheted synthetic fabrics</t>
   </si>
   <si>
-    <t>Manufacture of hats, caps and other clothing accessories such as gloves,</t>
-  </si>
-  <si>
     <t>Manufacture of wearing apparel n.e.c.</t>
   </si>
   <si>
     <t>Manufacture of fur and skin rugs and other similar articles</t>
   </si>
   <si>
-    <t>Manufacture of knitted or crocheted wearing apparel and other made-up</t>
-  </si>
-  <si>
-    <t>Manufacture of purse, ladies’ handbags, artistic leather presented articles</t>
-  </si>
-  <si>
     <t>Manufacture of imitation jewellery and related articles</t>
   </si>
   <si>
-    <t>Wholesale of edible oils, fats, sugar and processed/manufactured spices</t>
-  </si>
-  <si>
     <t>Wholesale of tea, coffee &amp; cocoa</t>
   </si>
   <si>
-    <t>Wholesale of textiles, fabrics, yarn, household linen, articles of clothing,</t>
-  </si>
-  <si>
     <t>Wholesale of umbrella and clothing accessories</t>
   </si>
   <si>
@@ -116,12 +101,6 @@
     <t>Retail sale of wallpaper and floor coverings</t>
   </si>
   <si>
-    <t>Retail sale of household utensils and cutlery, crockery, glassware, china and</t>
-  </si>
-  <si>
-    <t>Retail sale of readymade garments, hosiery goods, other articles of clothing</t>
-  </si>
-  <si>
     <t>Retail sale of footwear</t>
   </si>
   <si>
@@ -141,6 +120,33 @@
   </si>
   <si>
     <t>Retail sale via stalls and markets of textiles, clothing and footwear</t>
+  </si>
+  <si>
+    <t>Manufacture of hats, caps and other clothing accessories such as gloves, 
+belts, ties, cravats, hairnets etc.</t>
+  </si>
+  <si>
+    <t>Manufacture of knitted or crocheted wearing apparel and other made-up 
+articles directly into shape (pullovers, cardigans, jerseys, waistcoats and 
+similar articles)</t>
+  </si>
+  <si>
+    <t>Manufacture of purse, ladies’ handbags, artistic leather presented articles 
+and novelties</t>
+  </si>
+  <si>
+    <t>Wholesale of edible oils, fats, sugar and processed/manufactured spices etc.</t>
+  </si>
+  <si>
+    <t>Wholesale of textiles, fabrics, yarn, household linen, articles of clothing, 
+floor coverings and tapestry, sports clothes</t>
+  </si>
+  <si>
+    <t>Retail sale of household utensils and cutlery, crockery, glassware, china and pottery</t>
+  </si>
+  <si>
+    <t>Retail sale of readymade garments, hosiery goods, other articles of clothing 
+and clothing accessories such as gloves, ties, braces etc.</t>
   </si>
 </sst>
 </file>
@@ -176,10 +182,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -554,12 +563,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>14103</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -567,7 +576,7 @@
         <v>14109</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -575,23 +584,23 @@
         <v>14202</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>14301</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>15122</v>
       </c>
-      <c r="B9" t="s">
-        <v>9</v>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -599,7 +608,7 @@
         <v>32120</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -607,7 +616,7 @@
         <v>46305</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -615,15 +624,15 @@
         <v>46306</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46411</v>
       </c>
-      <c r="B13" t="s">
-        <v>13</v>
+      <c r="B13" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -631,7 +640,7 @@
         <v>46412</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -639,7 +648,7 @@
         <v>46413</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -647,7 +656,7 @@
         <v>46419</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -655,7 +664,7 @@
         <v>47190</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -663,7 +672,7 @@
         <v>47211</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -671,7 +680,7 @@
         <v>47214</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -679,7 +688,7 @@
         <v>47215</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -687,7 +696,7 @@
         <v>47219</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -695,7 +704,7 @@
         <v>47510</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -703,7 +712,7 @@
         <v>47531</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -711,7 +720,7 @@
         <v>47532</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -719,15 +728,15 @@
         <v>47592</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>47711</v>
       </c>
-      <c r="B26" t="s">
-        <v>26</v>
+      <c r="B26" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -735,7 +744,7 @@
         <v>47713</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -743,7 +752,7 @@
         <v>47722</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -751,7 +760,7 @@
         <v>47732</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -759,7 +768,7 @@
         <v>47733</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -767,7 +776,7 @@
         <v>47734</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -775,7 +784,7 @@
         <v>47735</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -783,7 +792,7 @@
         <v>47820</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
